--- a/testakten/befristungskontrollklage-vogt-stadtwerke/streitwert_annahmeverzug_berechnung.xlsx
+++ b/testakten/befristungskontrollklage-vogt-stadtwerke/streitwert_annahmeverzug_berechnung.xlsx
@@ -530,6 +530,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -631,6 +632,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -722,10 +724,11 @@
         <v>8850</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>C. Annahmeverzugslohn § 615 BGB (fiktive Berechnung)</t>
+          <t>C. Annahmeverzugslohn § 615 BGB (vorläufige Berechnung)</t>
         </is>
       </c>
     </row>
@@ -927,7 +930,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Summe (6 Monate fiktiv)</t>
+          <t>Summe (6 Monate vorläufig)</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr"/>
@@ -942,6 +945,7 @@
         <v>10998.6</v>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
@@ -980,7 +984,7 @@
     <row r="40" ht="14" customHeight="1">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>• Fiktive Berechnung: Wird ggf. monatlich fortgeschrieben bis zum Gütertermin.</t>
+          <t>Vorläufige Berechnung: Die Fortschreibung erfolgt monatlich bis zum Gütertermin.</t>
         </is>
       </c>
     </row>
